--- a/data/trans_dic/P16A05-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A05-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -727,52 +727,52 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 2,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,12</t>
+          <t>1,28; 3,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,27</t>
+          <t>0,23; 2,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,08</t>
+          <t>0,93; 4,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,19</t>
+          <t>0,0; 4,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,35</t>
+          <t>0,78; 2,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,46</t>
+          <t>0,3; 1,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,48</t>
+          <t>0,73; 2,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,93</t>
+          <t>0,99; 2,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,99</t>
+          <t>1,27; 4,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,26</t>
+          <t>1,01; 3,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,86</t>
+          <t>0,38; 3,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,88</t>
+          <t>0,81; 2,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,13</t>
+          <t>1,42; 4,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,09</t>
+          <t>1,47; 3,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,56</t>
+          <t>0,7; 3,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,54</t>
+          <t>1,13; 2,46</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,73</t>
+          <t>1,62; 3,6</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,11</t>
+          <t>1,47; 3,12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,86</t>
+          <t>0,88; 2,95</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,55</t>
+          <t>0,6; 2,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,66</t>
+          <t>1,76; 4,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,59</t>
+          <t>1,82; 4,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,21</t>
+          <t>1,97; 4,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,66</t>
+          <t>2,65; 5,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,29; 7,9</t>
+          <t>4,09; 7,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 7,37</t>
+          <t>3,96; 7,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,84</t>
+          <t>3,69; 6,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 3,72</t>
+          <t>1,84; 3,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,27; 5,65</t>
+          <t>3,34; 5,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,21; 5,39</t>
+          <t>3,24; 5,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 5,51</t>
+          <t>3,14; 5,33</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,88</t>
+          <t>1,74; 5,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 6,2</t>
+          <t>2,76; 6,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,69; 6,01</t>
+          <t>2,63; 5,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 7,68</t>
+          <t>2,01; 7,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,9; 9,17</t>
+          <t>4,81; 9,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,56; 11,34</t>
+          <t>6,6; 11,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,7; 10,28</t>
+          <t>5,84; 10,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,49; 11,02</t>
+          <t>6,48; 10,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,71; 6,48</t>
+          <t>3,57; 6,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,11; 8,13</t>
+          <t>5,2; 8,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 7,25</t>
+          <t>4,58; 7,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,65; 8,26</t>
+          <t>3,97; 8,43</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 7,0</t>
+          <t>2,5; 6,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,44</t>
+          <t>1,91; 5,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,08; 8,91</t>
+          <t>4,33; 9,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,28; 7,99</t>
+          <t>4,19; 7,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,38; 10,68</t>
+          <t>5,29; 10,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,16; 14,09</t>
+          <t>8,25; 13,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,25; 16,74</t>
+          <t>10,34; 16,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,37; 14,67</t>
+          <t>10,34; 14,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,41; 7,84</t>
+          <t>4,48; 8,07</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,69; 9,01</t>
+          <t>5,68; 8,94</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,99; 12,03</t>
+          <t>7,95; 12,13</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,68; 10,35</t>
+          <t>7,6; 10,47</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,01; 8,02</t>
+          <t>2,94; 8,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,93; 8,89</t>
+          <t>2,97; 8,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,67</t>
+          <t>2,35; 6,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,42; 7,09</t>
+          <t>3,44; 7,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,95; 14,26</t>
+          <t>8,05; 14,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,29; 14,92</t>
+          <t>8,11; 14,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,57; 16,25</t>
+          <t>9,15; 16,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,56; 14,12</t>
+          <t>3,65; 14,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,27; 10,33</t>
+          <t>6,33; 10,37</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,38; 10,95</t>
+          <t>6,46; 10,72</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,61; 10,75</t>
+          <t>6,65; 10,87</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,18; 10,12</t>
+          <t>3,94; 10,11</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,99; 10,81</t>
+          <t>4,26; 11,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,41; 13,3</t>
+          <t>4,36; 12,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,59; 9,19</t>
+          <t>3,92; 9,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,83; 11,16</t>
+          <t>5,93; 11,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,28; 11,51</t>
+          <t>5,4; 11,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,32; 17,27</t>
+          <t>9,98; 17,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,09; 16,1</t>
+          <t>8,51; 16,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,19; 19,4</t>
+          <t>14,09; 19,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,63; 10,23</t>
+          <t>5,41; 10,31</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,68; 14,2</t>
+          <t>8,82; 13,9</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,44; 12,38</t>
+          <t>7,61; 12,61</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,55; 15,27</t>
+          <t>11,51; 15,1</t>
         </is>
       </c>
     </row>
@@ -1697,47 +1697,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,21</t>
+          <t>2,07; 3,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,02</t>
+          <t>2,76; 4,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,96; 4,24</t>
+          <t>2,87; 4,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,21; 4,9</t>
+          <t>3,3; 4,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,61; 6,14</t>
+          <t>4,6; 6,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,35; 8,0</t>
+          <t>6,22; 8,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,72; 8,55</t>
+          <t>6,78; 8,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,33; 8,89</t>
+          <t>6,57; 8,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,54; 4,54</t>
+          <t>3,5; 4,46</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1747,12 +1747,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,02; 6,15</t>
+          <t>5,05; 6,18</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,29; 6,77</t>
+          <t>5,26; 6,74</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6452</t>
+          <t>0; 6488</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>815; 6775</t>
+          <t>815; 6805</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 8381</t>
+          <t>0; 8864</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4435</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5881; 19257</t>
+          <t>5977; 18629</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>992; 9742</t>
+          <t>997; 9697</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4011; 16153</t>
+          <t>3674; 16732</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 13119</t>
+          <t>0; 14641</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7812; 22563</t>
+          <t>7526; 21794</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2767; 12852</t>
+          <t>2673; 12489</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5395; 20236</t>
+          <t>5922; 20023</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 12726</t>
+          <t>0; 10766</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7177; 21560</t>
+          <t>7317; 21574</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8680; 27390</t>
+          <t>8686; 27751</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5946; 19277</t>
+          <t>5939; 19081</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1806; 16350</t>
+          <t>1620; 15144</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5002; 18012</t>
+          <t>5073; 18577</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8455; 25186</t>
+          <t>8659; 25295</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8429; 23057</t>
+          <t>8272; 22017</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3440; 18232</t>
+          <t>3594; 18073</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15536; 34576</t>
+          <t>15440; 33483</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20698; 48280</t>
+          <t>21008; 46662</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16901; 35866</t>
+          <t>16960; 36019</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7922; 26757</t>
+          <t>8264; 27619</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3793; 16278</t>
+          <t>3822; 16853</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11950; 31696</t>
+          <t>11952; 31954</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11874; 30691</t>
+          <t>12149; 30680</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10855; 27943</t>
+          <t>10591; 26756</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17424; 39061</t>
+          <t>18276; 39239</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30338; 55860</t>
+          <t>28917; 54700</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25923; 48756</t>
+          <t>26215; 49385</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19580; 37095</t>
+          <t>20020; 37468</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25386; 49398</t>
+          <t>24399; 50014</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45350; 78400</t>
+          <t>46321; 77092</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42679; 71683</t>
+          <t>43094; 72147</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34553; 59452</t>
+          <t>33882; 57518</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9202; 25321</t>
+          <t>9033; 26006</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16714; 38083</t>
+          <t>16988; 39212</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17389; 38821</t>
+          <t>17013; 36896</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16362; 68149</t>
+          <t>17806; 68190</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25267; 47295</t>
+          <t>24778; 48901</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40318; 69654</t>
+          <t>40526; 69277</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36982; 66694</t>
+          <t>37898; 65928</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>46295; 78593</t>
+          <t>46174; 77924</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38343; 67041</t>
+          <t>36946; 66053</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62847; 99854</t>
+          <t>63893; 101050</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>59568; 93854</t>
+          <t>59304; 94580</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>58363; 132255</t>
+          <t>63594; 134940</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9546; 27077</t>
+          <t>9662; 26279</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8434; 23306</t>
+          <t>8162; 23636</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19491; 42579</t>
+          <t>20671; 43638</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24000; 44747</t>
+          <t>23498; 44046</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>21736; 43151</t>
+          <t>21382; 42717</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36546; 63090</t>
+          <t>36955; 62443</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50906; 83152</t>
+          <t>51351; 80593</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>56428; 79835</t>
+          <t>56267; 79208</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>34902; 61997</t>
+          <t>35445; 63796</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49825; 78916</t>
+          <t>49734; 78331</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>77874; 117304</t>
+          <t>77459; 118245</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>84872; 114288</t>
+          <t>83936; 115695</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8799; 23454</t>
+          <t>8603; 23504</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9066; 27546</t>
+          <t>9187; 27316</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7666; 22299</t>
+          <t>7845; 22351</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12601; 26102</t>
+          <t>12670; 25867</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27264; 48893</t>
+          <t>27594; 49877</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29273; 52661</t>
+          <t>28617; 50156</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36146; 61378</t>
+          <t>34557; 62316</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>21632; 85926</t>
+          <t>22217; 86729</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>39820; 65633</t>
+          <t>40240; 65896</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>42269; 72579</t>
+          <t>42820; 71090</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>47103; 76583</t>
+          <t>47386; 77420</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>40833; 98861</t>
+          <t>38459; 98757</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>8382; 22681</t>
+          <t>8933; 23202</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>10994; 33131</t>
+          <t>10866; 31365</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9234; 23613</t>
+          <t>10070; 23969</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16465; 31488</t>
+          <t>16751; 31456</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>17635; 38421</t>
+          <t>18027; 38239</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>39931; 66781</t>
+          <t>38584; 67485</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36392; 64443</t>
+          <t>34062; 65205</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>60201; 82332</t>
+          <t>59807; 82538</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>30602; 55616</t>
+          <t>29403; 56054</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>55189; 90309</t>
+          <t>56079; 88360</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>48918; 81353</t>
+          <t>49979; 82847</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>81641; 107886</t>
+          <t>81359; 106684</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>68210; 105061</t>
+          <t>67807; 103312</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>92671; 137543</t>
+          <t>94380; 141186</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>100365; 144005</t>
+          <t>97572; 140507</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>111138; 169391</t>
+          <t>114257; 169604</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>155861; 207406</t>
+          <t>155481; 207452</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>225291; 283634</t>
+          <t>220617; 285627</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>238343; 303133</t>
+          <t>240366; 304472</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>231360; 325044</t>
+          <t>240418; 327373</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>235596; 301929</t>
+          <t>233080; 297133</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>329798; 410502</t>
+          <t>329289; 410329</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>348475; 426976</t>
+          <t>350080; 429092</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>376179; 481945</t>
+          <t>373970; 479385</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A05-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A05-Edad-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,5</t>
+          <t>0,18; 1,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,11</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,98</t>
+          <t>1,19; 4,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,26</t>
+          <t>0,23; 2,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,23</t>
+          <t>0,92; 4,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,67</t>
+          <t>0,0; 3,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,27</t>
+          <t>0,77; 2,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,42</t>
+          <t>0,33; 1,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,46</t>
+          <t>0,58; 2,37</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,93</t>
+          <t>1,03; 3,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,04</t>
+          <t>1,32; 4,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,23</t>
+          <t>1,0; 3,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,58</t>
+          <t>0,64; 3,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,97</t>
+          <t>0,81; 2,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,15</t>
+          <t>1,35; 4,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,91</t>
+          <t>1,5; 4,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,53</t>
+          <t>0,94; 3,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,46</t>
+          <t>1,13; 2,64</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,6</t>
+          <t>1,6; 3,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,12</t>
+          <t>1,48; 3,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,95</t>
+          <t>0,97; 3,01</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,64</t>
+          <t>0,57; 2,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,7</t>
+          <t>1,78; 4,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,59</t>
+          <t>1,84; 4,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,99</t>
+          <t>1,85; 4,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,69</t>
+          <t>2,61; 5,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,09; 7,74</t>
+          <t>4,09; 7,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,96; 7,47</t>
+          <t>3,98; 7,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,69; 6,91</t>
+          <t>3,37; 6,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,77</t>
+          <t>1,92; 3,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,56</t>
+          <t>3,3; 5,64</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,24; 5,42</t>
+          <t>3,23; 5,39</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,14; 5,33</t>
+          <t>2,95; 4,85</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,01</t>
+          <t>1,63; 4,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 6,38</t>
+          <t>2,76; 6,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,71</t>
+          <t>2,66; 5,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 7,68</t>
+          <t>4,55; 8,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,81; 9,48</t>
+          <t>4,8; 9,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,6; 11,28</t>
+          <t>6,58; 11,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,84; 10,16</t>
+          <t>5,63; 10,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,48; 10,93</t>
+          <t>6,26; 9,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 6,38</t>
+          <t>3,61; 6,48</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,2; 8,22</t>
+          <t>5,12; 8,15</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,58; 7,3</t>
+          <t>4,61; 7,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,97; 8,43</t>
+          <t>5,99; 8,65</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 6,8</t>
+          <t>2,62; 6,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,91; 5,52</t>
+          <t>1,98; 5,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,33; 9,13</t>
+          <t>4,29; 8,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,19; 7,86</t>
+          <t>4,22; 7,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,29; 10,57</t>
+          <t>5,42; 10,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,25; 13,94</t>
+          <t>7,96; 14,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,34; 16,22</t>
+          <t>10,18; 16,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,34; 14,55</t>
+          <t>10,01; 14,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,48; 8,07</t>
+          <t>4,65; 8,0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,68; 8,94</t>
+          <t>5,63; 9,31</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,95; 12,13</t>
+          <t>7,98; 11,85</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,6; 10,47</t>
+          <t>7,73; 10,36</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,94; 8,03</t>
+          <t>2,93; 8,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,97; 8,82</t>
+          <t>2,98; 8,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,35; 6,69</t>
+          <t>2,21; 6,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,44; 7,03</t>
+          <t>3,29; 6,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,05; 14,54</t>
+          <t>8,0; 14,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,11; 14,21</t>
+          <t>7,98; 14,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,15; 16,5</t>
+          <t>9,38; 16,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,65; 14,26</t>
+          <t>11,84; 16,51</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,33; 10,37</t>
+          <t>6,29; 10,44</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,46; 10,72</t>
+          <t>6,21; 10,7</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,65; 10,87</t>
+          <t>6,55; 11,19</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,94; 10,11</t>
+          <t>8,15; 11,22</t>
         </is>
       </c>
     </row>
@@ -1504,14 +1504,14 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
+          <t>8,08%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>8,18%</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t>13,47%</t>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,26; 11,05</t>
+          <t>3,98; 11,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,36; 12,59</t>
+          <t>4,57; 12,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,92; 9,33</t>
+          <t>3,65; 9,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,93; 11,14</t>
+          <t>5,8; 10,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,4; 11,45</t>
+          <t>5,44; 11,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,98; 17,45</t>
+          <t>9,91; 17,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,51; 16,29</t>
+          <t>8,8; 16,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,09; 19,45</t>
+          <t>14,45; 20,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,41; 10,31</t>
+          <t>5,56; 10,5</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,82; 13,9</t>
+          <t>8,73; 14,1</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,61; 12,61</t>
+          <t>7,44; 12,54</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,51; 15,1</t>
+          <t>11,5; 15,39</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -1697,32 +1697,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,15</t>
+          <t>2,11; 3,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,13</t>
+          <t>2,66; 4,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,87; 4,14</t>
+          <t>2,94; 4,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,3; 4,9</t>
+          <t>3,65; 5,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,6; 6,14</t>
+          <t>4,53; 6,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,22; 8,05</t>
+          <t>6,26; 8,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1732,27 +1732,27 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,57; 8,95</t>
+          <t>7,74; 9,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,5; 4,46</t>
+          <t>3,49; 4,43</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,73; 5,89</t>
+          <t>4,75; 5,93</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,05; 6,18</t>
+          <t>5,0; 6,15</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,26; 6,74</t>
+          <t>5,89; 6,9</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>2448</t>
         </is>
       </c>
     </row>
@@ -2068,17 +2068,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6488</t>
+          <t>0; 6565</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>815; 6805</t>
+          <t>811; 7713</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 8864</t>
+          <t>0; 8143</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2088,42 +2088,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5977; 18629</t>
+          <t>5567; 19642</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>997; 9697</t>
+          <t>994; 9818</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3674; 16732</t>
+          <t>3653; 15937</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 14641</t>
+          <t>0; 12666</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7526; 21794</t>
+          <t>7451; 21832</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2673; 12489</t>
+          <t>2920; 12007</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5922; 20023</t>
+          <t>4745; 19288</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 10766</t>
+          <t>0; 14738</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6080</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>9890</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15509</t>
+          <t>17191</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7317; 21574</t>
+          <t>7550; 22280</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8686; 27751</t>
+          <t>9081; 28754</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5939; 19081</t>
+          <t>5877; 18858</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1620; 15144</t>
+          <t>3029; 17082</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5073; 18577</t>
+          <t>5094; 18489</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8659; 25295</t>
+          <t>8239; 25054</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8272; 22017</t>
+          <t>8461; 23762</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3594; 18073</t>
+          <t>4710; 19219</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15440; 33483</t>
+          <t>15409; 35880</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21008; 46662</t>
+          <t>20786; 45441</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16960; 36019</t>
+          <t>17031; 35260</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8264; 27619</t>
+          <t>9450; 29432</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17928</t>
+          <t>18272</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27350</t>
+          <t>29664</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>45278</t>
+          <t>47937</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3822; 16853</t>
+          <t>3651; 15594</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11952; 31954</t>
+          <t>12083; 33130</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12149; 30680</t>
+          <t>12292; 32154</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10591; 26756</t>
+          <t>11475; 30398</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18276; 39239</t>
+          <t>17983; 38330</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28917; 54700</t>
+          <t>28899; 53564</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26215; 49385</t>
+          <t>26323; 50380</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20020; 37468</t>
+          <t>20988; 39738</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>24399; 50014</t>
+          <t>25518; 49612</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46321; 77092</t>
+          <t>45785; 78260</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>43094; 72147</t>
+          <t>42941; 71715</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33882; 57518</t>
+          <t>36624; 60248</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43667</t>
+          <t>44876</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>59039</t>
+          <t>57874</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>102705</t>
+          <t>102750</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9033; 26006</t>
+          <t>8462; 25364</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16988; 39212</t>
+          <t>16934; 38761</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17013; 36896</t>
+          <t>17183; 37525</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17806; 68190</t>
+          <t>31870; 61026</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24778; 48901</t>
+          <t>24771; 46800</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40526; 69277</t>
+          <t>40406; 70348</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37898; 65928</t>
+          <t>36557; 66296</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>46174; 77924</t>
+          <t>46102; 70910</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>36946; 66053</t>
+          <t>37306; 67095</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>63893; 101050</t>
+          <t>62899; 100164</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>59304; 94580</t>
+          <t>59714; 94965</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>63594; 134940</t>
+          <t>86046; 124344</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32229</t>
+          <t>34892</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>67068</t>
+          <t>74116</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99298</t>
+          <t>109008</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9662; 26279</t>
+          <t>10142; 26422</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8162; 23636</t>
+          <t>8474; 24281</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20671; 43638</t>
+          <t>20508; 42194</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23498; 44046</t>
+          <t>25682; 46475</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>21382; 42717</t>
+          <t>21901; 43411</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36955; 62443</t>
+          <t>35660; 62971</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>51351; 80593</t>
+          <t>50562; 82536</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>56267; 79208</t>
+          <t>60759; 86135</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35445; 63796</t>
+          <t>36762; 63240</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49734; 78331</t>
+          <t>49287; 81588</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>77459; 118245</t>
+          <t>77783; 115514</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>83936; 115695</t>
+          <t>93927; 125830</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18720</t>
+          <t>20063</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>54402</t>
+          <t>61210</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>73122</t>
+          <t>81273</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8603; 23504</t>
+          <t>8580; 23744</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9187; 27316</t>
+          <t>9226; 27689</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7845; 22351</t>
+          <t>7373; 22525</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12670; 25867</t>
+          <t>13413; 28089</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27594; 49877</t>
+          <t>27446; 50036</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28617; 50156</t>
+          <t>28183; 51802</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34557; 62316</t>
+          <t>35418; 61664</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>22217; 86729</t>
+          <t>52013; 72504</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>40240; 65896</t>
+          <t>39998; 66349</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>42820; 71090</t>
+          <t>41185; 70945</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>47386; 77420</t>
+          <t>46673; 79693</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>38459; 98757</t>
+          <t>69007; 94952</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23089</t>
+          <t>25035</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>71063</t>
+          <t>78886</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94153</t>
+          <t>103921</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>8933; 23202</t>
+          <t>8351; 23257</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>10866; 31365</t>
+          <t>11384; 31526</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10070; 23969</t>
+          <t>9381; 24262</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16751; 31456</t>
+          <t>17976; 33459</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>18027; 38239</t>
+          <t>18178; 39301</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38584; 67485</t>
+          <t>38336; 68012</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34062; 65205</t>
+          <t>35201; 66241</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>59807; 82538</t>
+          <t>66905; 93274</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>29403; 56054</t>
+          <t>30219; 57074</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>56079; 88360</t>
+          <t>55503; 89658</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>49979; 82847</t>
+          <t>48923; 82400</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>81359; 106684</t>
+          <t>88871; 118939</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>141714</t>
+          <t>150440</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>290887</t>
+          <t>314087</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>432601</t>
+          <t>464527</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>67807; 103312</t>
+          <t>69233; 104896</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>94380; 141186</t>
+          <t>91134; 138415</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>97572; 140507</t>
+          <t>99860; 142104</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>114257; 169604</t>
+          <t>128724; 176451</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>155481; 207452</t>
+          <t>153029; 205573</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>220617; 285627</t>
+          <t>222140; 287276</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>240366; 304472</t>
+          <t>240175; 304450</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>240418; 327373</t>
+          <t>288698; 344031</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>233080; 297133</t>
+          <t>232017; 294823</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>329289; 410329</t>
+          <t>330772; 412982</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>350080; 429092</t>
+          <t>347022; 426620</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>373970; 479385</t>
+          <t>428107; 501395</t>
         </is>
       </c>
     </row>
